--- a/source_data/Figure2.xlsx
+++ b/source_data/Figure2.xlsx
@@ -195,10 +195,10 @@
     <t>Chikungunya</t>
   </si>
   <si>
+    <t>decreasing</t>
+  </si>
+  <si>
     <t>Zika</t>
-  </si>
-  <si>
-    <t>decreasing</t>
   </si>
 </sst>
 </file>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -785,16 +785,16 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>0.05454545454545454</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="F6">
-        <v>0.8762696636277618</v>
+        <v>0.7554968749288828</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -881,16 +881,16 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>0.2363636363636364</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="F9">
-        <v>0.3502013891792957</v>
+        <v>0.2757578478275093</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0.9713531249085637</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>0.9455437507840984</v>
+        <v>0.930682736417844</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>26</v>
       </c>
       <c r="E29">
-        <v>0.1272727272727273</v>
+        <v>-0.1272727272727273</v>
       </c>
       <c r="F29">
         <v>0.640428787412791</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0.8645788630072678</v>
+        <v>0.7859807845520617</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0.8645788630072678</v>
+        <v>0.7859807845520617</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -1585,16 +1585,16 @@
         <v>26</v>
       </c>
       <c r="E31">
-        <v>-0.3454545454545455</v>
+        <v>-0.2</v>
       </c>
       <c r="F31">
-        <v>0.1611249492890519</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0.4833748478671556</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -1617,16 +1617,16 @@
         <v>26</v>
       </c>
       <c r="E32">
-        <v>-0.05454545454545454</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="F32">
-        <v>0.8762696636277618</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0.9463712367179828</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -1649,16 +1649,16 @@
         <v>26</v>
       </c>
       <c r="E33">
-        <v>-0.01818181818181818</v>
+        <v>-0.09090909090909091</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0.7554968749288828</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0.8499339842949932</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -1678,19 +1678,19 @@
         <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E34">
-        <v>-0.05454545454545454</v>
+        <v>-0.5636363636363636</v>
       </c>
       <c r="F34">
-        <v>0.8762696636277618</v>
+        <v>0.01951748118217767</v>
       </c>
       <c r="G34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0.9463712367179828</v>
+        <v>0.1317429979796992</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -1713,16 +1713,16 @@
         <v>26</v>
       </c>
       <c r="E35">
-        <v>0.1272727272727273</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="F35">
-        <v>0.640428787412791</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0.8645788630072678</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>0.4833748478671556</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -1777,16 +1777,16 @@
         <v>50</v>
       </c>
       <c r="E37">
-        <v>0.5272727272727272</v>
+        <v>0.6</v>
       </c>
       <c r="F37">
-        <v>0.02927250918630464</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>0.2634525826767418</v>
+        <v>0.1317429979796992</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -1809,16 +1809,16 @@
         <v>26</v>
       </c>
       <c r="E38">
-        <v>-0.1272727272727273</v>
+        <v>-0.2727272727272727</v>
       </c>
       <c r="F38">
-        <v>0.640428787412791</v>
+        <v>0.2757578478275093</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>0.8645788630072678</v>
+        <v>0.5318187065244823</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -1841,16 +1841,16 @@
         <v>26</v>
       </c>
       <c r="E39">
-        <v>0.05454545454545454</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="F39">
-        <v>0.8762696636277618</v>
+        <v>0.7554968749288828</v>
       </c>
       <c r="G39" t="b">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>0.9463712367179828</v>
+        <v>0.8499339842949932</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -1873,19 +1873,19 @@
         <v>50</v>
       </c>
       <c r="E40">
-        <v>0.6727272727272727</v>
+        <v>0.7818181818181819</v>
       </c>
       <c r="F40">
-        <v>0.005069309556701596</v>
+        <v>0.001076632864587701</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
       </c>
       <c r="H40">
-        <v>0.1368713580309431</v>
+        <v>0.02906908734386793</v>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40">
         <v>11</v>
@@ -1914,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>0.2634525826767418</v>
+        <v>0.1317429979796992</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -1937,16 +1937,16 @@
         <v>26</v>
       </c>
       <c r="E42">
-        <v>-0.2727272727272727</v>
+        <v>-0.4181818181818182</v>
       </c>
       <c r="F42">
-        <v>0.2757578478275093</v>
+        <v>0.0867681727038756</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0.620455157611896</v>
+        <v>0.3904567771674402</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>26</v>
       </c>
       <c r="E43">
-        <v>0.2</v>
+        <v>-0.4181818181818182</v>
       </c>
       <c r="F43">
-        <v>0.4362749288405292</v>
+        <v>0.0867681727038756</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0.8413873627638778</v>
+        <v>0.3904567771674402</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -2001,16 +2001,16 @@
         <v>26</v>
       </c>
       <c r="E44">
-        <v>0.1272727272727273</v>
+        <v>0.3090909090909091</v>
       </c>
       <c r="F44">
-        <v>0.640428787412791</v>
+        <v>0.2129119028115045</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0.8645788630072678</v>
+        <v>0.4422016443008171</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -2033,16 +2033,16 @@
         <v>26</v>
       </c>
       <c r="E45">
-        <v>0.01818181818181818</v>
+        <v>-0.05454545454545454</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>0.8762696636277618</v>
       </c>
       <c r="G45" t="b">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0.9463712367179828</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -2065,16 +2065,16 @@
         <v>26</v>
       </c>
       <c r="E46">
-        <v>-0.1636363636363636</v>
+        <v>-0.2</v>
       </c>
       <c r="F46">
-        <v>0.5334165134726945</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>0.8645788630072678</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>26</v>
       </c>
       <c r="E47">
-        <v>-0.2727272727272727</v>
+        <v>-0.2363636363636364</v>
       </c>
       <c r="F47">
-        <v>0.2757578478275093</v>
+        <v>0.3502013891792957</v>
       </c>
       <c r="G47" t="b">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0.620455157611896</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -2129,16 +2129,16 @@
         <v>26</v>
       </c>
       <c r="E48">
-        <v>0.3454545454545455</v>
+        <v>0.3818181818181818</v>
       </c>
       <c r="F48">
-        <v>0.1611249492890519</v>
+        <v>0.1194709867717008</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0.4833748478671556</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -2161,16 +2161,16 @@
         <v>26</v>
       </c>
       <c r="E49">
-        <v>-0.2</v>
+        <v>-0.3090909090909091</v>
       </c>
       <c r="F49">
-        <v>0.4362749288405292</v>
+        <v>0.2129119028115045</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0.8413873627638778</v>
+        <v>0.4422016443008171</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -2193,16 +2193,16 @@
         <v>26</v>
       </c>
       <c r="E50">
-        <v>0.3454545454545455</v>
+        <v>0.2</v>
       </c>
       <c r="F50">
-        <v>0.1611249492890519</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>0.4833748478671556</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -2225,16 +2225,16 @@
         <v>26</v>
       </c>
       <c r="E51">
-        <v>-0.3090909090909091</v>
+        <v>-0.2</v>
       </c>
       <c r="F51">
-        <v>0.2129119028115045</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="G51" t="b">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0.5748621375910622</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -2257,16 +2257,16 @@
         <v>26</v>
       </c>
       <c r="E52">
-        <v>0.3818181818181818</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="F52">
-        <v>0.1194709867717008</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0.4833748478671556</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -2289,16 +2289,16 @@
         <v>26</v>
       </c>
       <c r="E53">
-        <v>0.3818181818181818</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="F53">
-        <v>0.1194709867717008</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0.4833748478671556</v>
+        <v>0.3954885118913091</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -2321,16 +2321,16 @@
         <v>26</v>
       </c>
       <c r="E54">
-        <v>-0.05454545454545454</v>
+        <v>-0.2</v>
       </c>
       <c r="F54">
-        <v>0.8762696636277618</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0.9463712367179828</v>
+        <v>0.5889711539347144</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -2353,16 +2353,16 @@
         <v>26</v>
       </c>
       <c r="E55">
-        <v>-0.05454545454545454</v>
+        <v>-0.01818181818181818</v>
       </c>
       <c r="F55">
-        <v>0.8762696636277618</v>
+        <v>1</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>0.9463712367179828</v>
+        <v>1</v>
       </c>
       <c r="I55" t="b">
         <v>0</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
         <v>24</v>
@@ -2385,16 +2385,16 @@
         <v>26</v>
       </c>
       <c r="E56">
-        <v>0.1636363636363636</v>
+        <v>-0.05454545454545454</v>
       </c>
       <c r="F56">
-        <v>0.5334165134726945</v>
+        <v>0.8762696636277618</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>0.6858212316077501</v>
+        <v>0.9099723429980604</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="s">
         <v>27</v>
@@ -2414,22 +2414,22 @@
         <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E57">
-        <v>-0.5272727272727272</v>
+        <v>-0.6</v>
       </c>
       <c r="F57">
-        <v>0.02927250918630464</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
       </c>
       <c r="H57">
-        <v>0.1317262913383709</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57">
         <v>11</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58" t="s">
         <v>29</v>
@@ -2449,16 +2449,16 @@
         <v>26</v>
       </c>
       <c r="E58">
-        <v>0.05454545454545454</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="F58">
-        <v>0.8762696636277618</v>
+        <v>1</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>0.9099723429980604</v>
+        <v>1</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
         <v>30</v>
@@ -2478,22 +2478,22 @@
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E59">
-        <v>-0.4545454545454545</v>
+        <v>-0.6</v>
       </c>
       <c r="F59">
-        <v>0.06170669002831275</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="G59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>0.2380115186806349</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <v>11</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
         <v>31</v>
@@ -2510,19 +2510,19 @@
         <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E60">
-        <v>-0.3090909090909091</v>
+        <v>-0.4909090909090909</v>
       </c>
       <c r="F60">
-        <v>0.2129119028115045</v>
+        <v>0.04296014602842502</v>
       </c>
       <c r="G60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>0.3832414250607081</v>
+        <v>0.0892249186744212</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
         <v>32</v>
@@ -2545,16 +2545,16 @@
         <v>26</v>
       </c>
       <c r="E61">
-        <v>0.05454545454545454</v>
+        <v>-0.3454545454545455</v>
       </c>
       <c r="F61">
-        <v>0.8762696636277618</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="G61" t="b">
         <v>0</v>
       </c>
       <c r="H61">
-        <v>0.9099723429980604</v>
+        <v>0.2416874239335778</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
         <v>33</v>
@@ -2574,22 +2574,22 @@
         <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E62">
-        <v>-0.6363636363636364</v>
+        <v>-0.7818181818181819</v>
       </c>
       <c r="F62">
-        <v>0.008123423304273514</v>
+        <v>0.001076632864587701</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>0.1096662146076924</v>
+        <v>0.01453454367193396</v>
       </c>
       <c r="I62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62">
         <v>11</v>
@@ -2597,7 +2597,7 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B63" t="s">
         <v>35</v>
@@ -2606,22 +2606,22 @@
         <v>36</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E63">
-        <v>-0.02222222222222222</v>
+        <v>-0.6</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>0.02004466862262744</v>
       </c>
       <c r="G63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>0.04510050440091173</v>
       </c>
       <c r="I63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63">
         <v>10</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B64" t="s">
         <v>37</v>
@@ -2638,22 +2638,22 @@
         <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E64">
-        <v>-0.3090909090909091</v>
+        <v>-0.6727272727272727</v>
       </c>
       <c r="F64">
-        <v>0.2129119028115045</v>
+        <v>0.005069309556701596</v>
       </c>
       <c r="G64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>0.3832414250607081</v>
+        <v>0.02737427160618862</v>
       </c>
       <c r="I64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64">
         <v>11</v>
@@ -2661,7 +2661,7 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
         <v>38</v>
@@ -2673,16 +2673,16 @@
         <v>26</v>
       </c>
       <c r="E65">
-        <v>0.1636363636363636</v>
+        <v>-0.2</v>
       </c>
       <c r="F65">
-        <v>0.5334165134726945</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="G65" t="b">
         <v>0</v>
       </c>
       <c r="H65">
-        <v>0.6858212316077501</v>
+        <v>0.5354283217588313</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
         <v>39</v>
@@ -2705,16 +2705,16 @@
         <v>26</v>
       </c>
       <c r="E66">
-        <v>-0.2</v>
+        <v>-0.3090909090909091</v>
       </c>
       <c r="F66">
-        <v>0.4362749288405292</v>
+        <v>0.2129119028115045</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>0.619969635720752</v>
+        <v>0.3025590197847696</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
         <v>40</v>
@@ -2737,16 +2737,16 @@
         <v>26</v>
       </c>
       <c r="E67">
-        <v>0.3090909090909091</v>
+        <v>-0.2</v>
       </c>
       <c r="F67">
-        <v>0.2129119028115045</v>
+        <v>0.4362749288405292</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
       </c>
       <c r="H67">
-        <v>0.3832414250607081</v>
+        <v>0.5354283217588313</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B68" t="s">
         <v>41</v>
@@ -2766,22 +2766,22 @@
         <v>36</v>
       </c>
       <c r="D68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E68">
-        <v>-0.5636363636363636</v>
+        <v>-0.6363636363636364</v>
       </c>
       <c r="F68">
-        <v>0.01951748118217767</v>
+        <v>0.008123423304273514</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>0.1317262913383709</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="I68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68">
         <v>11</v>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B69" t="s">
         <v>42</v>
@@ -2798,22 +2798,22 @@
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E69">
-        <v>-0.2727272727272727</v>
+        <v>-0.6</v>
       </c>
       <c r="F69">
-        <v>0.2757578478275093</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="G69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>0.4379683465495736</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="I69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69">
         <v>11</v>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B70" t="s">
         <v>43</v>
@@ -2830,22 +2830,22 @@
         <v>28</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E70">
-        <v>-0.3454545454545455</v>
+        <v>-0.5636363636363636</v>
       </c>
       <c r="F70">
-        <v>0.1611249492890519</v>
+        <v>0.01951748118217767</v>
       </c>
       <c r="G70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>0.3625311359003667</v>
+        <v>0.04510050440091173</v>
       </c>
       <c r="I70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70">
         <v>11</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B71" t="s">
         <v>44</v>
@@ -2862,22 +2862,22 @@
         <v>45</v>
       </c>
       <c r="D71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E71">
-        <v>-0.5272727272727272</v>
+        <v>-0.6727272727272727</v>
       </c>
       <c r="F71">
-        <v>0.02927250918630464</v>
+        <v>0.005069309556701596</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>0.1317262913383709</v>
+        <v>0.02737427160618862</v>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71">
         <v>11</v>
@@ -2885,7 +2885,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B72" t="s">
         <v>46</v>
@@ -2897,16 +2897,16 @@
         <v>26</v>
       </c>
       <c r="E72">
-        <v>0.2</v>
+        <v>-0.1636363636363636</v>
       </c>
       <c r="F72">
-        <v>0.4362749288405292</v>
+        <v>0.5334165134726945</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
       </c>
       <c r="H72">
-        <v>0.619969635720752</v>
+        <v>0.5760898345505101</v>
       </c>
       <c r="I72" t="b">
         <v>0</v>
@@ -2917,7 +2917,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B73" t="s">
         <v>47</v>
@@ -2926,22 +2926,22 @@
         <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E73">
-        <v>-0.6363636363636364</v>
+        <v>-0.6</v>
       </c>
       <c r="F73">
-        <v>0.008123423304273514</v>
+        <v>0.01273136426992361</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>0.1096662146076924</v>
+        <v>0.03437468352879374</v>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73">
         <v>11</v>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B74" t="s">
         <v>48</v>
@@ -2961,16 +2961,16 @@
         <v>26</v>
       </c>
       <c r="E74">
-        <v>0.09090909090909091</v>
+        <v>-0.1636363636363636</v>
       </c>
       <c r="F74">
-        <v>0.7554968749288828</v>
+        <v>0.5334165134726945</v>
       </c>
       <c r="G74" t="b">
         <v>0</v>
       </c>
       <c r="H74">
-        <v>0.8499339842949932</v>
+        <v>0.5760898345505101</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B75" t="s">
         <v>49</v>
@@ -2993,16 +2993,16 @@
         <v>26</v>
       </c>
       <c r="E75">
-        <v>-0.3818181818181818</v>
+        <v>-0.3454545454545455</v>
       </c>
       <c r="F75">
-        <v>0.1194709867717008</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="G75" t="b">
         <v>0</v>
       </c>
       <c r="H75">
-        <v>0.3225716642835921</v>
+        <v>0.2416874239335778</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B76" t="s">
         <v>51</v>
@@ -3022,22 +3022,22 @@
         <v>36</v>
       </c>
       <c r="D76" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E76">
-        <v>-0.5636363636363636</v>
+        <v>-0.9454545454545454</v>
       </c>
       <c r="F76">
-        <v>0.01951748118217767</v>
+        <v>5.939321753611893E-05</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>0.1317262913383709</v>
+        <v>0.001603616873475211</v>
       </c>
       <c r="I76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76">
         <v>11</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B77" t="s">
         <v>52</v>
@@ -3057,16 +3057,16 @@
         <v>26</v>
       </c>
       <c r="E77">
-        <v>0.2727272727272727</v>
+        <v>-0.3454545454545455</v>
       </c>
       <c r="F77">
-        <v>0.2757578478275093</v>
+        <v>0.1611249492890519</v>
       </c>
       <c r="G77" t="b">
         <v>0</v>
       </c>
       <c r="H77">
-        <v>0.4379683465495736</v>
+        <v>0.2416874239335778</v>
       </c>
       <c r="I77" t="b">
         <v>0</v>
@@ -3077,7 +3077,7 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B78" t="s">
         <v>53</v>
@@ -3089,16 +3089,16 @@
         <v>26</v>
       </c>
       <c r="E78">
-        <v>-0.3454545454545455</v>
+        <v>-0.3818181818181818</v>
       </c>
       <c r="F78">
-        <v>0.1611249492890519</v>
+        <v>0.1194709867717008</v>
       </c>
       <c r="G78" t="b">
         <v>0</v>
       </c>
       <c r="H78">
-        <v>0.3625311359003667</v>
+        <v>0.2150477761890614</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B79" t="s">
         <v>54</v>
@@ -3121,16 +3121,16 @@
         <v>26</v>
       </c>
       <c r="E79">
-        <v>-0.09090909090909091</v>
+        <v>-0.2727272727272727</v>
       </c>
       <c r="F79">
-        <v>0.7554968749288828</v>
+        <v>0.2757578478275093</v>
       </c>
       <c r="G79" t="b">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>0.8499339842949932</v>
+        <v>0.3722730945671376</v>
       </c>
       <c r="I79" t="b">
         <v>0</v>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B80" t="s">
         <v>55</v>
@@ -3150,22 +3150,22 @@
         <v>36</v>
       </c>
       <c r="D80" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E80">
-        <v>-0.3818181818181818</v>
+        <v>-0.7090909090909091</v>
       </c>
       <c r="F80">
-        <v>0.1194709867717008</v>
+        <v>0.003093449322761233</v>
       </c>
       <c r="G80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80">
-        <v>0.3225716642835921</v>
+        <v>0.02737427160618862</v>
       </c>
       <c r="I80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80">
         <v>11</v>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B81" t="s">
         <v>56</v>
@@ -3185,16 +3185,16 @@
         <v>26</v>
       </c>
       <c r="E81">
-        <v>0.09090909090909091</v>
+        <v>-0.1636363636363636</v>
       </c>
       <c r="F81">
-        <v>0.7554968749288828</v>
+        <v>0.5334165134726945</v>
       </c>
       <c r="G81" t="b">
         <v>0</v>
       </c>
       <c r="H81">
-        <v>0.8499339842949932</v>
+        <v>0.5760898345505101</v>
       </c>
       <c r="I81" t="b">
         <v>0</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
         <v>57</v>
@@ -3217,16 +3217,16 @@
         <v>26</v>
       </c>
       <c r="E82">
-        <v>-0.4181818181818182</v>
+        <v>-0.4545454545454545</v>
       </c>
       <c r="F82">
-        <v>0.0867681727038756</v>
+        <v>0.06170669002831275</v>
       </c>
       <c r="G82" t="b">
         <v>0</v>
       </c>
       <c r="H82">
-        <v>0.2928425828755802</v>
+        <v>0.1190057593403174</v>
       </c>
       <c r="I82" t="b">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3267,10 +3267,10 @@
         <v>11.32803348169427</v>
       </c>
       <c r="C2">
-        <v>1.88799552863405</v>
+        <v>-0.2735588329307728</v>
       </c>
       <c r="D2">
-        <v>5.201483689539216</v>
+        <v>-0.2193499075591784</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3281,10 +3281,10 @@
         <v>15.82813249442329</v>
       </c>
       <c r="C3">
-        <v>1.929879640341924</v>
+        <v>1.973474081493142</v>
       </c>
       <c r="D3">
-        <v>-1.223698183262965</v>
+        <v>-0.8812606367287721</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3295,10 +3295,10 @@
         <v>5.253917306952189</v>
       </c>
       <c r="C4">
-        <v>-6.205119843407868</v>
+        <v>-2.558710576002405</v>
       </c>
       <c r="D4">
-        <v>0.1073480995923699</v>
+        <v>0.01052558895807554</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3309,10 +3309,10 @@
         <v>-0.7143485256943336</v>
       </c>
       <c r="C5">
-        <v>-0.237995351762246</v>
+        <v>0.01050994528115634</v>
       </c>
       <c r="D5">
-        <v>-1.49480678961878</v>
+        <v>-1.166090323755766</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3323,10 +3323,10 @@
         <v>12.29804292220766</v>
       </c>
       <c r="C6">
-        <v>-1.128634712152777</v>
+        <v>-2.947744029334416</v>
       </c>
       <c r="D6">
-        <v>-1.724191049650246</v>
+        <v>-1.797893960349319</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3334,13 +3334,13 @@
         <v>32</v>
       </c>
       <c r="B7">
-        <v>-25.1958354910948</v>
+        <v>-25.07256730607227</v>
       </c>
       <c r="C7">
-        <v>-2.376434052457029</v>
+        <v>-2.228797948318025</v>
       </c>
       <c r="D7">
-        <v>0.7046674133388144</v>
+        <v>-0.3463926746117606</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3351,10 +3351,10 @@
         <v>39.83410814867079</v>
       </c>
       <c r="C8">
-        <v>0.6751647044356626</v>
+        <v>1.109201995922639</v>
       </c>
       <c r="D8">
-        <v>-1.131010454359694</v>
+        <v>-0.318203772046579</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3362,13 +3362,13 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>60.26697272766927</v>
+        <v>51.82729044141305</v>
       </c>
       <c r="C9">
-        <v>17.99883157716391</v>
+        <v>6.7131117056469</v>
       </c>
       <c r="D9">
-        <v>-0.7107909252082804</v>
+        <v>-1.912873237103457</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3379,10 +3379,10 @@
         <v>51.15440655881628</v>
       </c>
       <c r="C10">
-        <v>12.02840796326513</v>
+        <v>8.617580373632418</v>
       </c>
       <c r="D10">
-        <v>-3.715745054080492</v>
+        <v>-1.810720555627992</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3393,10 +3393,10 @@
         <v>4.842665304938926</v>
       </c>
       <c r="C11">
-        <v>-5.064432508662249</v>
+        <v>-3.623710463999429</v>
       </c>
       <c r="D11">
-        <v>1.929532137585396</v>
+        <v>-0.3699955048688119</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3407,10 +3407,10 @@
         <v>60.54271852946994</v>
       </c>
       <c r="C12">
-        <v>4.264841360995097</v>
+        <v>1.827756078009721</v>
       </c>
       <c r="D12">
-        <v>-1.365576859815874</v>
+        <v>-1.194211812546458</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3421,10 +3421,10 @@
         <v>-137.2287223491217</v>
       </c>
       <c r="C13">
-        <v>158.2381810484503</v>
+        <v>15.70346941651842</v>
       </c>
       <c r="D13">
-        <v>5.771986424590998</v>
+        <v>-0.1992511491900825</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3432,13 +3432,13 @@
         <v>41</v>
       </c>
       <c r="B14">
-        <v>28.8018048092385</v>
+        <v>29.18425068373712</v>
       </c>
       <c r="C14">
-        <v>13.4912660482552</v>
+        <v>10.17643495220999</v>
       </c>
       <c r="D14">
-        <v>-0.8242533106763592</v>
+        <v>-0.3699213159603518</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3446,13 +3446,13 @@
         <v>42</v>
       </c>
       <c r="B15">
-        <v>6.675769969497495</v>
+        <v>6.80644941501278</v>
       </c>
       <c r="C15">
-        <v>-6.290549945004511</v>
+        <v>-5.223625993828157</v>
       </c>
       <c r="D15">
-        <v>-0.8700077196283497</v>
+        <v>-0.4219131176919373</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3463,10 +3463,10 @@
         <v>-13.52546766381079</v>
       </c>
       <c r="C16">
-        <v>1.312797127663078</v>
+        <v>-4.654990769883248</v>
       </c>
       <c r="D16">
-        <v>-2.052022542788601</v>
+        <v>-1.616720649837422</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3477,10 +3477,10 @@
         <v>110.5277281403091</v>
       </c>
       <c r="C17">
-        <v>1.230822536333226</v>
+        <v>0.3259454295923828</v>
       </c>
       <c r="D17">
-        <v>-0.3187158780675844</v>
+        <v>-0.0422227519853562</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3491,10 +3491,10 @@
         <v>-0.2244810925143123</v>
       </c>
       <c r="C18">
-        <v>0.3219345441494182</v>
+        <v>-0.221433219376887</v>
       </c>
       <c r="D18">
-        <v>1.527475463215183</v>
+        <v>-0.1319235636535279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3505,10 +3505,10 @@
         <v>39.1200863420067</v>
       </c>
       <c r="C19">
-        <v>-4.962274999737982</v>
+        <v>-3.666382029996921</v>
       </c>
       <c r="D19">
-        <v>-0.6747996311100496</v>
+        <v>-0.2829370814975902</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3516,13 +3516,13 @@
         <v>48</v>
       </c>
       <c r="B20">
-        <v>-50.72043139210189</v>
+        <v>-50.47503169807199</v>
       </c>
       <c r="C20">
-        <v>-20.97829234924756</v>
+        <v>-19.00409982565504</v>
       </c>
       <c r="D20">
-        <v>1.078953589110945</v>
+        <v>-0.8500269406817593</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3533,10 +3533,10 @@
         <v>54.38479600607688</v>
       </c>
       <c r="C21">
-        <v>0.5017752893508248</v>
+        <v>0.2366864085983684</v>
       </c>
       <c r="D21">
-        <v>-0.1883944983551364</v>
+        <v>-0.04021433875215356</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3544,13 +3544,13 @@
         <v>51</v>
       </c>
       <c r="B22">
-        <v>-0.9676203685337575</v>
+        <v>-0.9667603126735602</v>
       </c>
       <c r="C22">
-        <v>-4.848973085877031</v>
+        <v>-4.816873394037015</v>
       </c>
       <c r="D22">
-        <v>-2.496310605478456</v>
+        <v>-1.926855737509735</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3561,10 +3561,10 @@
         <v>3.20121445615527</v>
       </c>
       <c r="C23">
-        <v>11.04515380771469</v>
+        <v>1.293033500920147</v>
       </c>
       <c r="D23">
-        <v>2.690581337962379</v>
+        <v>-0.5839479430430228</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3575,10 +3575,10 @@
         <v>5.282856121633259</v>
       </c>
       <c r="C24">
-        <v>-5.207962723243465</v>
+        <v>-0.1781542748160071</v>
       </c>
       <c r="D24">
-        <v>-3.037658223343728</v>
+        <v>-0.893811789220924</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3589,10 +3589,10 @@
         <v>51.653660532096</v>
       </c>
       <c r="C25">
-        <v>0.9576327922959754</v>
+        <v>0.1675317483546054</v>
       </c>
       <c r="D25">
-        <v>-0.07083273711645129</v>
+        <v>-0.03979407691186252</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3603,10 +3603,10 @@
         <v>119.044010071151</v>
       </c>
       <c r="C26">
-        <v>2.363778198315053</v>
+        <v>0.7495155064633311</v>
       </c>
       <c r="D26">
-        <v>-0.2642831506577579</v>
+        <v>-0.1131228514685746</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3614,13 +3614,13 @@
         <v>56</v>
       </c>
       <c r="B27">
-        <v>-2.946864739012744</v>
+        <v>-2.571238002190559</v>
       </c>
       <c r="C27">
-        <v>-5.120842894912045</v>
+        <v>-10.89915101949616</v>
       </c>
       <c r="D27">
-        <v>0.518834885629095</v>
+        <v>-0.2106418610824311</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3631,10 +3631,10 @@
         <v>4.106238658562029</v>
       </c>
       <c r="C28">
-        <v>-1.251441975056784</v>
+        <v>-0.9987992136124246</v>
       </c>
       <c r="D28">
-        <v>-16.01094594835849</v>
+        <v>-2.778856561134424</v>
       </c>
     </row>
   </sheetData>
